--- a/output/2026-10-03_03_Malesia_Pahang_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-10-03_03_Malesia_Pahang_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -493,11 +493,9 @@
           <t>Metalworking / Lavorazioni Metalliche - Distributore utensili, hardware industriale e materiale elettrico</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Esistenza confermata: profilo fornitore verificato su marketplace B2B Lapasar, SSM Reg. CA0203857H / 201303295436, sede B116 Perkampungan Setali, Jalan Haji Ahmad, 25300 Kuantan, Pahang. Nessun sito web proprietario reperito (solo profilo marketplace); nessun telefono/email diretti reperiti (solo canale di contatto del marketplace Lapasar, non dell'azienda).</t>
+          <t>Esistenza confermata: profilo fornitore verificato su marketplace B2B Lapasar, SSM Reg. CA0203857H / 201303295436, sede B116 Perkampungan Setali, Jalan Haji Ahmad, 25300 Kuantan, Pahang. Nessun sito web proprietario reperito (solo profilo marketplace); nessun telefono/email diretti reperiti (solo canale di contatto del marketplace Lapasar, non dell'azienda). [DUPLICATO — vedi anche: 2026-10-03_02_Malesia_Pahang_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -544,7 +542,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>

--- a/output/2026-10-03_03_Malesia_Pahang_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-10-03_03_Malesia_Pahang_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -537,7 +537,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Azienda attiva dal 1979 (43 anni), sede e fabbrica su 6 acri a Lot 73-75, Semambu Industrial Estate, 25350 Kuantan, Pahang. Confermata tramite sito ufficiale. Non confermato se tratti anche dust collector/aspiratori oltre a compressori e trattamento aria: verificare gamma prodotti completa con l'azienda.</t>
+          <t>Azienda attiva dal 1979 (43 anni), sede e fabbrica su 6 acri a Lot 73-75, Semambu Industrial Estate, 25350 Kuantan, Pahang. Confermata tramite sito ufficiale. Non confermato se tratti anche dust collector/aspiratori oltre a compressori e trattamento aria: verificare gamma prodotti completa con l'azienda. [DUPLICATO — vedi anche: 2026-10-02_21_Malesia_Pahang_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
